--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -1305,6 +1305,11 @@
           <t>上面能放一堆器械的大墙</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>unlock_wall_tier3</t>
+        </is>
+      </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
@@ -1526,6 +1531,11 @@
       <c r="N20" t="inlineStr">
         <is>
           <t>厚石墙仓储建筑，储重物抗风雪</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>unlock_stone_warehouse</t>
         </is>
       </c>
     </row>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -642,10 +642,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>90</v>
       </c>
       <c r="G7" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>500</v>
@@ -848,10 +848,10 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -902,13 +902,13 @@
         <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>600</v>
@@ -956,13 +956,13 @@
         <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>350</v>
@@ -1005,13 +1005,13 @@
         <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="H11" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>500</v>
@@ -1059,13 +1059,13 @@
         <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="I12" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
         <v>700</v>
@@ -1113,13 +1113,13 @@
         <v>180</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="H13" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -1167,10 +1167,10 @@
         <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1225,13 +1225,13 @@
         <v>90</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
         <v>800</v>
@@ -1283,13 +1283,13 @@
         <v>180</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="I16" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
         <v>2000</v>
@@ -1346,13 +1346,13 @@
         <v>120</v>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
         <v>500</v>
@@ -1462,10 +1462,10 @@
         <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
         <v>650</v>
@@ -1565,13 +1565,13 @@
         <v>150</v>
       </c>
       <c r="G21" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H21" t="n">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="I21" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
         <v>700</v>
@@ -1614,13 +1614,13 @@
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H22" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
         <v>450</v>
@@ -1663,13 +1663,13 @@
         <v>200</v>
       </c>
       <c r="G23" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="H23" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="I23" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
         <v>900</v>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -642,10 +642,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>90</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
         <v>500</v>
@@ -848,13 +848,13 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>250</v>
@@ -902,13 +902,13 @@
         <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
         <v>600</v>
@@ -956,13 +956,13 @@
         <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>350</v>
@@ -1005,13 +1005,13 @@
         <v>90</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
         <v>500</v>
@@ -1059,13 +1059,13 @@
         <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J12" t="n">
         <v>700</v>
@@ -1113,13 +1113,13 @@
         <v>180</v>
       </c>
       <c r="G13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -1167,10 +1167,10 @@
         <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1225,13 +1225,13 @@
         <v>90</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>800</v>
@@ -1283,13 +1283,13 @@
         <v>180</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
         <v>2000</v>
@@ -1346,13 +1346,13 @@
         <v>120</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>500</v>
@@ -1462,10 +1462,10 @@
         <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
         <v>650</v>
@@ -1565,13 +1565,13 @@
         <v>150</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
         <v>700</v>
@@ -1614,13 +1614,13 @@
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
         <v>450</v>
@@ -1663,13 +1663,13 @@
         <v>200</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H23" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
         <v>900</v>
